--- a/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstCaptialAccount001.xlsx
+++ b/tams-invest-parent/tams-invest-basicdata/src/main/resources/tpl/MstCaptialAccount001.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ideaWorkSpace\2.1.0\tams-invest-parent\tams-invest-basicdata\src\main\resources\tpl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workSpaceGZNEW\tams\tams-invest-parent\tams-invest-basicdata\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13245" windowHeight="3450"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="13250" windowHeight="3450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,12 +23,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
-    <t>账户</t>
-  </si>
-  <si>
-    <t>账户名称</t>
-  </si>
-  <si>
     <t>开户银行</t>
   </si>
   <si>
@@ -42,12 +36,20 @@
     <t>Swift Code</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>账号</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>账户名称</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -62,6 +64,12 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -395,35 +403,35 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:F1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="40.125" customWidth="1"/>
-    <col min="2" max="2" width="49.625" customWidth="1"/>
-    <col min="3" max="3" width="46.875" customWidth="1"/>
+    <col min="1" max="1" width="40.08984375" customWidth="1"/>
+    <col min="2" max="2" width="49.6328125" customWidth="1"/>
+    <col min="3" max="3" width="46.90625" customWidth="1"/>
     <col min="4" max="4" width="50" customWidth="1"/>
     <col min="5" max="5" width="36" customWidth="1"/>
-    <col min="6" max="6" width="28.375" customWidth="1"/>
-    <col min="7" max="7" width="49.125" customWidth="1"/>
+    <col min="6" max="6" width="28.36328125" customWidth="1"/>
+    <col min="7" max="7" width="49.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F1" t="s">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -435,7 +443,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -445,7 +453,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
